--- a/downloads/ecommerce-calculators.xlsx
+++ b/downloads/ecommerce-calculators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yjbab\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E6FEBC9-6693-4C0B-9DB5-5CCA5071C737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AFA45D5-EDEA-4A15-9EC5-FCF5E7B563DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,23 +954,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="177" formatCode="#,##0;[Red]\(#,##0\);0"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
+    <numFmt numFmtId="179" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,##0&quot; 원&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="17"/>
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
@@ -983,7 +979,93 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF255CBA"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF255CBA"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF64748B"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF64748B"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="21"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="21"/>
+      <color rgb="FF172C43"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF255CBA"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF172C43"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
@@ -999,7 +1081,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1026,6 +1108,26 @@
         <fgColor rgb="FFE5F3EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF172C43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF1FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1038,29 +1140,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="15" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="37">
     <dxf>
       <font>
         <color rgb="FFA02E26"/>
@@ -1093,11 +1284,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA02E26"/>
+        <color rgb="FFAA3529"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4DE"/>
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1113,11 +1304,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA02E26"/>
+        <color rgb="FFAA3529"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4DE"/>
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1133,11 +1324,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA02E26"/>
+        <color rgb="FFAA3529"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4DE"/>
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1153,11 +1344,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA02E26"/>
+        <color rgb="FFAA3529"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4DE"/>
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1173,11 +1364,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA02E26"/>
+        <color rgb="FFAA3529"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4DE"/>
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1193,11 +1384,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA02E26"/>
+        <color rgb="FFAA3529"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4DE"/>
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1213,11 +1404,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFA02E26"/>
+        <color rgb="FFAA3529"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4DE"/>
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1233,6 +1424,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFA02E26"/>
       </font>
       <fill>
@@ -1243,11 +1444,171 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFA02E26"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA02E26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA02E26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA02E26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA02E26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA02E26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA02E26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA02E26"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4DE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFAA3529"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE3DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1344,7 +1705,7 @@
             <c:numRef>
               <c:f>목표판매가!$E$5:$E$11</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>20787</c:v>
@@ -1373,7 +1734,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A9A6-4F21-8F0A-B2575F89A12B}"/>
+              <c16:uniqueId val="{00000000-5ED9-4DB6-8796-C0592B93A507}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1534,7 +1895,7 @@
             <c:numRef>
               <c:f>행사손익분기!$E$5:$E$10</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>-28000</c:v>
@@ -1560,7 +1921,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4FC3-49A1-9CFB-68F75D67A3F0}"/>
+              <c16:uniqueId val="{00000000-3FAC-4866-8B9E-12FD9E81233B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1621,7 +1982,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1734,6 +2095,26 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductComparison" displayName="ProductComparison" ref="A9:L19" totalsRowShown="0">
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="상품"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="판매가 원"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="원가 원"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="수수료 %"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="배송포장 원"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="주문 건"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="광고비 원"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="주문 기여금 원"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="기여율 %"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="매출 원"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="광고 전 합계 원"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="광고 후 합계 원"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1952,25 +2333,25 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="28.05" customHeight="1">
+    <row r="2" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" ht="28.05" customHeight="1">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" ht="28.05" customHeight="1">
       <c r="A4" s="1"/>
@@ -1982,239 +2363,239 @@
     </row>
     <row r="5" spans="1:6" ht="28.05" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="33" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="13" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" ht="28.05" customHeight="1">
+    <row r="7" spans="1:6" ht="33" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="1:6" ht="33" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="13" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" ht="28.05" customHeight="1">
+      <c r="E8" s="16"/>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="1:6" ht="33" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:6" ht="33" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="13" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" ht="28.05" customHeight="1">
+      <c r="E10" s="16"/>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="1:6" ht="33" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="13" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="28.05" customHeight="1">
+    <row r="13" spans="1:6" ht="33" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="28.05" customHeight="1">
+    <row r="14" spans="1:6" ht="33" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="13" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" ht="33" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" ht="28.05" customHeight="1">
+    <row r="16" spans="1:6" ht="33" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="33" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" ht="28.05" customHeight="1">
+    <row r="18" spans="1:6" ht="33" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="13" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" ht="28.05" customHeight="1">
+    <row r="19" spans="1:6" ht="33" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F19" s="17"/>
+    </row>
+    <row r="20" spans="1:6" ht="33" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F20" s="17"/>
+    </row>
+    <row r="21" spans="1:6" ht="33" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="14" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" ht="28.05" customHeight="1">
+      <c r="F21" s="17"/>
+    </row>
+    <row r="22" spans="1:6" ht="33" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="13" t="s">
         <v>46</v>
       </c>
       <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="1"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" spans="1:6" ht="28.05" customHeight="1">
       <c r="A23" s="1"/>
@@ -2281,7 +2662,7 @@
       <c r="F30" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B6" location="'001'!A1" display="001  마진과 주문 손익 →" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B7" location="'002'!A1" display="002  할인 행사 손익 →" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -2316,224 +2697,224 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B17,1)=0,B14&gt;0,B15&lt;=B14),(B14-B15)*B16-B15*B17,"입력 확인"),"입력 확인")</f>
         <v>889000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B17,1)=0,B14&gt;0,B15&lt;=B14),B14*B16-B5,"입력 확인"),"입력 확인")</f>
         <v>81000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B17,1)=0,B14&gt;0,B15&lt;=B14),B15/B14*100,"입력 확인"),"입력 확인")</f>
         <v>5</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>100</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>5</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="19" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>9700</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>6500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2552,12 +2933,21 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="decimal" sqref="B14:B17" xr:uid="{00000000-0002-0000-0900-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
   </hyperlinks>
@@ -2573,218 +2963,218 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,B16&lt;=100),B14*B15,"입력 확인"),"입력 확인")</f>
         <v>100000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,B16&lt;=100),B5*B16/100,"입력 확인"),"입력 확인")</f>
         <v>60000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,B16&lt;=100),B5*(1-B16/100),"입력 확인"),"입력 확인")</f>
         <v>40000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>100</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>1000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="24">
         <v>60</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2803,12 +3193,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="17" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B14:B15" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B16" xr:uid="{00000000-0002-0000-0A00-000002000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
   </hyperlinks>
@@ -2824,229 +3227,229 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B14*B16/100,"입력 확인"),"입력 확인")</f>
         <v>20</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B14*B15,"입력 확인"),"입력 확인")</f>
         <v>500000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B5*B17-B6,"입력 확인"),"입력 확인")</f>
         <v>100000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" ht="45" customHeight="1">
+      <c r="A8" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B15/B17*100,"입력 확인"),"입력 확인")</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>1000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>500</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="19" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="24">
         <v>2</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>30000</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3065,12 +3468,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B17 B14:B15" xr:uid="{00000000-0002-0000-0B00-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B16" xr:uid="{00000000-0002-0000-0B00-000002000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
   </hyperlinks>
@@ -3086,215 +3502,215 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B14&gt;0,B16&lt;=B14),B14*B15/100,"입력 확인"),"입력 확인")</f>
         <v>194</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B14&gt;0,B16&lt;=B14),(B14-B16)*B15/100,"입력 확인"),"입력 확인")</f>
         <v>134</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="25.95" customHeight="1">
+    <row r="7" spans="1:4" ht="28.95" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>9700</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="24">
         <v>2</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="19" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>3000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3313,12 +3729,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B14 B16" xr:uid="{00000000-0002-0000-0C00-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B15" xr:uid="{00000000-0002-0000-0C00-000001000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
   </hyperlinks>
@@ -3334,213 +3763,213 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B16,1)=0,B15&gt;0,B16&gt;0),B15/B16,"입력 확인"),"입력 확인")</f>
         <v>6</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B16,1)=0,B15&gt;0,B16&gt;0),B14/B5,"입력 확인"),"입력 확인")</f>
         <v>20</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="25.95" customHeight="1">
+    <row r="7" spans="1:4" ht="28.95" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>120</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>180</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>30</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3559,12 +3988,21 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="11" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="decimal" sqref="B14:B16" xr:uid="{00000000-0002-0000-0D00-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
   </hyperlinks>
@@ -3580,213 +4018,213 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B15,1)=0,MOD(B16,1)=0,B14&gt;0,B15&gt;0),B14*B15,"입력 확인"),"입력 확인")</f>
         <v>60</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B15,1)=0,MOD(B16,1)=0,B14&gt;0,B15&gt;0),ROUNDUP(ROUND(B5+B16,8),0),"입력 확인"),"입력 확인")</f>
         <v>90</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="25.95" customHeight="1">
+    <row r="7" spans="1:4" ht="28.95" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>6</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>10</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>30</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3805,12 +4243,21 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="decimal" sqref="B14:B16" xr:uid="{00000000-0002-0000-0E00-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
   </hyperlinks>
@@ -3826,218 +4273,218 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B14,"입력 확인"),"입력 확인")</f>
         <v>800000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B15-B16,"입력 확인"),"입력 확인")</f>
         <v>900000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B6-B5,"입력 확인"),"입력 확인")</f>
         <v>100000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>800000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>1100000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>200000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4056,12 +4503,21 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="decimal" sqref="B14:B16" xr:uid="{00000000-0002-0000-0F00-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
   </hyperlinks>
@@ -4077,220 +4533,220 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B15&lt;=100,B17&lt;=100),B14*B15/100,"입력 확인"),"입력 확인")</f>
         <v>300000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B15&lt;=100,B17&lt;=100),B16*B17/100,"입력 확인"),"입력 확인")</f>
         <v>600000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B15&lt;=100,B17&lt;=100),B6-B5,"입력 확인"),"입력 확인")</f>
         <v>300000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>3000000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D14" s="19"/>
+    </row>
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="24">
         <v>10</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>2000000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="24">
         <v>30</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4309,12 +4765,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B14 B16" xr:uid="{00000000-0002-0000-1000-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B15 B17" xr:uid="{00000000-0002-0000-1000-000001000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
   </hyperlinks>
@@ -4330,232 +4799,232 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B17&lt;=100,MOD(B19,1)=0,B17&lt;100,B19&gt;0,B14*(1-B17/100)-B16-B18&gt;0,B15*(1-B17/100)-B16-B18&gt;0),B14*(1-B17/100)-B16-B18,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B17&lt;=100,MOD(B19,1)=0,B17&lt;100,B19&gt;0,B14*(1-B17/100)-B16-B18&gt;0,B15*(1-B17/100)-B16-B18&gt;0),B15*(1-B17/100)-B16-B18,"입력 확인"),"입력 확인")</f>
         <v>12520</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B17&lt;=100,MOD(B19,1)=0,B17&lt;100,B19&gt;0,B14*(1-B17/100)-B16-B18&gt;0,B15*(1-B17/100)-B16-B18&gt;0),ROUNDUP(ROUND(B5*B19/B6,8),0),"입력 확인"),"입력 확인")</f>
         <v>78</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>33000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>15000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="24">
         <v>6</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="23">
         <v>3500</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>100</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4574,12 +5043,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B18:B19 B14:B16" xr:uid="{00000000-0002-0000-1100-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B17" xr:uid="{00000000-0002-0000-1100-000003000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
   </hyperlinks>
@@ -4613,11 +5095,11 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="48" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -4636,36 +5118,36 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>249</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="28.05" customHeight="1">
+    <row r="5" spans="1:8" ht="42" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="27">
         <f>IFERROR(IF(AND(COUNT(B12:B17)=6,MIN(B12:B17)&gt;=0,B14+B15&lt;100,B17&lt;100),ROUNDUP(ROUND((B12+B13)/(1-(B14+B15)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>28907</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>5</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="29">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D5&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D5)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>20787</v>
       </c>
@@ -4673,19 +5155,19 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" ht="28.05" customHeight="1">
+    <row r="6" spans="1:8" ht="42" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="27">
         <f>IFERROR(IF(ISNUMBER(B5),ROUNDUP(ROUND((B12+B13+B16)/(1-B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>30320</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>10</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="29">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D6&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D6)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>22024</v>
       </c>
@@ -4693,19 +5175,19 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="28.05" customHeight="1">
+    <row r="7" spans="1:8" ht="42" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="27">
         <f>IFERROR(ROUNDUP(ROUND(B5/(1-B17/100),8),0),"입력 확인")</f>
         <v>32119</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>15</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="29">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D7&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D7)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>23418</v>
       </c>
@@ -4713,14 +5195,14 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="28.05" customHeight="1">
+    <row r="8" spans="1:8" ht="42" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="10"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>20</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="29">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D8&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D8)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>25000</v>
       </c>
@@ -4732,10 +5214,10 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>25</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="29">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D9&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D9)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>26812</v>
       </c>
@@ -4747,10 +5229,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>30</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="29">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D10&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D10)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>28907</v>
       </c>
@@ -4759,17 +5241,17 @@
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>35</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="29">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D11&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D11)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>31356</v>
       </c>
@@ -4863,7 +5345,7 @@
     </row>
     <row r="18" spans="1:8" ht="28.05" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="28"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -4873,7 +5355,7 @@
     </row>
     <row r="19" spans="1:8" ht="28.05" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -4882,10 +5364,10 @@
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="19"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -4894,10 +5376,10 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -4906,8 +5388,8 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -4916,8 +5398,8 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -5096,7 +5578,7 @@
       <c r="H40" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
@@ -5115,215 +5597,215 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0),(B14-B15)/B14*100,"입력 확인"),"입력 확인")</f>
         <v>50</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0),B14-B15-B14*B16/100-B17,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="25.95" customHeight="1">
+    <row r="7" spans="1:4" ht="28.95" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D14" s="19"/>
+    </row>
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="24">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>3500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5342,12 +5824,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="35" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B17 B14:B15" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B16" xr:uid="{00000000-0002-0000-0100-000002000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
@@ -5378,11 +5873,11 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="48" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -5401,36 +5896,36 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>261</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="28.05" customHeight="1">
+    <row r="5" spans="1:8" ht="42" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="27">
         <f>IFERROR(IF(AND(COUNT(B13:B19)=7,MIN(B13:B19)&gt;=0,B15&lt;100,MOD(B19,1)=0),B13*(1-B15/100)-B14-B16,"입력 확인"),"입력 확인")</f>
         <v>6880</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>25</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="29">
         <f t="shared" ref="E5:E10" si="0">IFERROR($B$5*D5-$B$17,"입력 확인")</f>
         <v>-28000</v>
       </c>
@@ -5438,19 +5933,19 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" ht="28.05" customHeight="1">
+    <row r="6" spans="1:8" ht="42" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="27">
         <f>IFERROR(IF(B5&gt;0,ROUNDUP(ROUND(B17/B5,8),0),"기여금 양수 필요"),"입력 확인")</f>
         <v>30</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>50</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="29">
         <f t="shared" si="0"/>
         <v>144000</v>
       </c>
@@ -5458,19 +5953,19 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="28.05" customHeight="1">
+    <row r="7" spans="1:8" ht="42" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="27">
         <f>IFERROR(IF(B5&gt;0,ROUNDUP(ROUND((B17+B18)/B5,8),0),"기여금 양수 필요"),"입력 확인")</f>
         <v>73</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>75</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="29">
         <f t="shared" si="0"/>
         <v>316000</v>
       </c>
@@ -5478,19 +5973,19 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="28.05" customHeight="1">
+    <row r="8" spans="1:8" ht="42" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="27">
         <f>IFERROR(B5*B19-B17,"입력 확인")</f>
         <v>488000</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="29">
         <f t="shared" si="0"/>
         <v>488000</v>
       </c>
@@ -5502,10 +5997,10 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>125</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="29">
         <f t="shared" si="0"/>
         <v>660000</v>
       </c>
@@ -5517,10 +6012,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>150</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="29">
         <f t="shared" si="0"/>
         <v>832000</v>
       </c>
@@ -5533,16 +6028,16 @@
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="30" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="1"/>
@@ -5651,8 +6146,8 @@
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -5661,8 +6156,8 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -5671,10 +6166,10 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="B22" s="1"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -5683,10 +6178,10 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="19"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -5865,7 +6360,7 @@
       <c r="H40" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
@@ -5904,21 +6399,21 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:13" ht="43.95" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="28.05" customHeight="1">
@@ -5941,7 +6436,7 @@
         <v>272</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="1">
+      <c r="C4" s="31">
         <f>IF(COUNT(L10:L19)=10,SUM(L10:L19),"입력 확인")</f>
         <v>8930000</v>
       </c>
@@ -5950,7 +6445,7 @@
         <v>273</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1">
+      <c r="G4" s="31">
         <f>IF(COUNT(J10:J19)=10,SUM(J10:J19),"입력 확인")</f>
         <v>34500000</v>
       </c>
@@ -6023,480 +6518,480 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:13" ht="42" customHeight="1">
+      <c r="A9" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="32" t="s">
         <v>286</v>
       </c>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:13" ht="33" customHeight="1">
+      <c r="A10" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="34">
         <v>30000</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="34">
         <v>15000</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="34">
         <v>6</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="34">
         <v>3500</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="34">
         <v>100</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="34">
         <v>500000</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="6">
         <f t="shared" ref="H10:H19" si="0">IFERROR(IF(AND(COUNT(B10:G10)=6,MIN(B10:G10)&gt;=0,B10&gt;0,D10&lt;100,MOD(F10,1)=0),B10*(1-D10/100)-C10-E10,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="7">
         <f t="shared" ref="I10:I19" si="1">IFERROR(H10/B10*100,"입력 확인")</f>
         <v>32.333333333333329</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="6">
         <f t="shared" ref="J10:J19" si="2">IFERROR(IF(ISNUMBER(H10),B10*F10,"입력 확인"),"입력 확인")</f>
         <v>3000000</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="6">
         <f t="shared" ref="K10:K19" si="3">IFERROR(H10*F10,"입력 확인")</f>
         <v>970000</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="6">
         <f t="shared" ref="L10:L19" si="4">IFERROR(K10-G10,"입력 확인")</f>
         <v>470000</v>
       </c>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:13" ht="33" customHeight="1">
+      <c r="A11" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="34">
         <v>31000</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="34">
         <v>15000</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="34">
         <v>6</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="34">
         <v>3500</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="34">
         <v>100</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="34">
         <v>500000</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6">
         <f t="shared" si="0"/>
         <v>10640</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="7">
         <f t="shared" si="1"/>
         <v>34.322580645161288</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="6">
         <f t="shared" si="2"/>
         <v>3100000</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="6">
         <f t="shared" si="3"/>
         <v>1064000</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="6">
         <f t="shared" si="4"/>
         <v>564000</v>
       </c>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:13" ht="33" customHeight="1">
+      <c r="A12" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="34">
         <v>32000</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="34">
         <v>15000</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="34">
         <v>6</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="34">
         <v>3500</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="34">
         <v>100</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="34">
         <v>500000</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="6">
         <f t="shared" si="0"/>
         <v>11580</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="7">
         <f t="shared" si="1"/>
         <v>36.1875</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="6">
         <f t="shared" si="2"/>
         <v>3200000</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="6">
         <f t="shared" si="3"/>
         <v>1158000</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="6">
         <f t="shared" si="4"/>
         <v>658000</v>
       </c>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:13" ht="33" customHeight="1">
+      <c r="A13" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="34">
         <v>33000</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="34">
         <v>15000</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="34">
         <v>6</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="34">
         <v>3500</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="34">
         <v>100</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="34">
         <v>500000</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="6">
         <f t="shared" si="0"/>
         <v>12520</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="7">
         <f t="shared" si="1"/>
         <v>37.939393939393938</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="6">
         <f t="shared" si="2"/>
         <v>3300000</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="6">
         <f t="shared" si="3"/>
         <v>1252000</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="6">
         <f t="shared" si="4"/>
         <v>752000</v>
       </c>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:13" ht="33" customHeight="1">
+      <c r="A14" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="34">
         <v>34000</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="34">
         <v>15000</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="34">
         <v>6</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="34">
         <v>3500</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="34">
         <v>100</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="34">
         <v>500000</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="6">
         <f t="shared" si="0"/>
         <v>13460</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="7">
         <f t="shared" si="1"/>
         <v>39.588235294117645</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="6">
         <f t="shared" si="2"/>
         <v>3400000</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="6">
         <f t="shared" si="3"/>
         <v>1346000</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="6">
         <f t="shared" si="4"/>
         <v>846000</v>
       </c>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:13" ht="33" customHeight="1">
+      <c r="A15" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="34">
         <v>35000</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="34">
         <v>15000</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="34">
         <v>6</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="34">
         <v>3500</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="34">
         <v>100</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="34">
         <v>500000</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="6">
         <f t="shared" si="0"/>
         <v>14400</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="7">
         <f t="shared" si="1"/>
         <v>41.142857142857139</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="6">
         <f t="shared" si="2"/>
         <v>3500000</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="6">
         <f t="shared" si="3"/>
         <v>1440000</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="6">
         <f t="shared" si="4"/>
         <v>940000</v>
       </c>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:13" ht="33" customHeight="1">
+      <c r="A16" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="34">
         <v>36000</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="34">
         <v>15000</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="34">
         <v>6</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="34">
         <v>3500</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="34">
         <v>100</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="34">
         <v>500000</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="6">
         <f t="shared" si="0"/>
         <v>15340</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="7">
         <f t="shared" si="1"/>
         <v>42.611111111111114</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="6">
         <f t="shared" si="2"/>
         <v>3600000</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="6">
         <f t="shared" si="3"/>
         <v>1534000</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="6">
         <f t="shared" si="4"/>
         <v>1034000</v>
       </c>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:13" ht="33" customHeight="1">
+      <c r="A17" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="34">
         <v>37000</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="34">
         <v>15000</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="34">
         <v>6</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="34">
         <v>3500</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="34">
         <v>100</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="34">
         <v>500000</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="6">
         <f t="shared" si="0"/>
         <v>16280</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="7">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="6">
         <f t="shared" si="2"/>
         <v>3700000</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="6">
         <f t="shared" si="3"/>
         <v>1628000</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="6">
         <f t="shared" si="4"/>
         <v>1128000</v>
       </c>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:13" ht="33" customHeight="1">
+      <c r="A18" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="34">
         <v>38000</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="34">
         <v>15000</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="34">
         <v>6</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="34">
         <v>3500</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="34">
         <v>100</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="34">
         <v>500000</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="6">
         <f t="shared" si="0"/>
         <v>17220</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="7">
         <f t="shared" si="1"/>
         <v>45.315789473684212</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="6">
         <f t="shared" si="2"/>
         <v>3800000</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="6">
         <f t="shared" si="3"/>
         <v>1722000</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="6">
         <f t="shared" si="4"/>
         <v>1222000</v>
       </c>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:13" ht="33" customHeight="1">
+      <c r="A19" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="34">
         <v>39000</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="34">
         <v>15000</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="34">
         <v>6</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="34">
         <v>3500</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="34">
         <v>100</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="34">
         <v>500000</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="6">
         <f t="shared" si="0"/>
         <v>18160</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="7">
         <f t="shared" si="1"/>
         <v>46.564102564102569</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="6">
         <f t="shared" si="2"/>
         <v>3900000</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="6">
         <f t="shared" si="3"/>
         <v>1816000</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="6">
         <f t="shared" si="4"/>
         <v>1316000</v>
       </c>
@@ -6670,13 +7165,26 @@
       <c r="M30" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="L10:L19">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>L10&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="whole" sqref="F10:F19" xr:uid="{00000000-0002-0000-1400-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="D10:D19" xr:uid="{00000000-0002-0000-1400-000001000000}">
+      <formula1>0</formula1>
+      <formula2>99.99</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -6688,230 +7196,230 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,B18&lt;=100,MOD(B19,1)=0,B14&gt;0,B18&lt;100,B14-B15-B14*B16/100-B17&gt;0,B14*(1-B18/100)*(1-B16/100)-B15-B17&gt;0),B14-B15-B14*B16/100-B17,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,B18&lt;=100,MOD(B19,1)=0,B14&gt;0,B18&lt;100,B14-B15-B14*B16/100-B17&gt;0,B14*(1-B18/100)*(1-B16/100)-B15-B17&gt;0),B14*(1-B18/100)*(1-B16/100)-B15-B17,"입력 확인"),"입력 확인")</f>
         <v>6880</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,B18&lt;=100,MOD(B19,1)=0,B14&gt;0,B18&lt;100,B14-B15-B14*B16/100-B17&gt;0,B14*(1-B18/100)*(1-B16/100)-B15-B17&gt;0),ROUNDUP(ROUND(B5*B19/B6,8),0),"입력 확인"),"입력 확인")</f>
         <v>141</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="24">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>3500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="24">
         <v>10</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>100</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -6930,12 +7438,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="33" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B19 B17 B14:B15" xr:uid="{00000000-0002-0000-0200-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B16 B18" xr:uid="{00000000-0002-0000-0200-000002000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
@@ -6951,221 +7472,221 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),B15*B14/100,"입력 확인"),"입력 확인")</f>
         <v>9699</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),B5-B16,"입력 확인"),"입력 확인")</f>
         <v>2199</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),10000/B14,"입력 확인"),"입력 확인")</f>
         <v>309.31023816888342</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" ht="45" customHeight="1">
+      <c r="A8" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),B15/B16*100,"입력 확인"),"입력 확인")</f>
         <v>400</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="24">
         <v>32.33</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D14" s="19"/>
+    </row>
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>30000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>7500</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7184,12 +7705,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="31" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B14" xr:uid="{00000000-0002-0000-0300-000000000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B15:B16" xr:uid="{00000000-0002-0000-0300-000001000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
@@ -7205,233 +7739,233 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),ROUNDUP(ROUND((B17+B15+B16)/(B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>30000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),ROUNDUP(ROUND(B18+B19/(B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>28572</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),ROUNDUP(ROUND(B19/(B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>8572</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" ht="45" customHeight="1">
+      <c r="A8" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),B18*B14/100+B19-B15-B16,"입력 확인"),"입력 확인")</f>
         <v>6500</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="24">
         <v>35</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D14" s="19"/>
+    </row>
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>3000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>500</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>7000</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="23">
         <v>20000</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>3000</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7450,12 +7984,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="29" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B14" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B15:B19" xr:uid="{00000000-0002-0000-0400-000001000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
@@ -7471,232 +8018,232 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100),B14-B15-B14*B16/100-B17-B18,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100),B19-B15-B17-B18,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100),B14-B14*B16/100-B19,"입력 확인"),"입력 확인")</f>
         <v>0</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="24">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>3000</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="23">
         <v>500</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>28200</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7715,12 +8262,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="27" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B17:B19 B14:B15" xr:uid="{00000000-0002-0000-0500-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B16" xr:uid="{00000000-0002-0000-0500-000002000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
   </hyperlinks>
@@ -7736,239 +8296,239 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),B18*(B14*(1-B16/100)-B15-B17),"입력 확인"),"입력 확인")</f>
         <v>19400</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),B19*(1-B16/100)-B18*B15-B17,"입력 확인"),"입력 확인")</f>
         <v>20080</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),B6-B5,"입력 확인"),"입력 확인")</f>
         <v>680</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" ht="45" customHeight="1">
+      <c r="A8" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),ROUNDUP(ROUND((B5+B18*B15+B17)/(1-B16/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>56277</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="24">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+    <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>3500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="23">
         <v>2</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>57000</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7987,12 +8547,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="25" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B17:B19 B14:B15" xr:uid="{00000000-0002-0000-0600-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B16" xr:uid="{00000000-0002-0000-0600-000002000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
@@ -8008,220 +8581,220 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B16&lt;=100,B14&gt;0,B15+B16&lt;=100),B14*(1-B15/100)*(1-B16/100),"입력 확인"),"입력 확인")</f>
         <v>24300</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B16&lt;=100,B14&gt;0,B15+B16&lt;=100),B14*(1-(B15+B16)/100),"입력 확인"),"입력 확인")</f>
         <v>24000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B16&lt;=100,B14&gt;0,B15+B16&lt;=100),(1-(1-B15/100)*(1-B16/100))*100,"입력 확인"),"입력 확인")</f>
         <v>18.999999999999993</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="19" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="e">
+      <c r="D13" s="19" t="e">
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="24">
         <v>10</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="19" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="24">
         <v>10</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -8240,12 +8813,25 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="23" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="decimal" sqref="B14" xr:uid="{00000000-0002-0000-0700-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" sqref="B15:B16" xr:uid="{00000000-0002-0000-0700-000001000000}">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
   </hyperlinks>
@@ -8261,219 +8847,219 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="5" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.95" customHeight="1">
+    <row r="1" spans="1:4" ht="28.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.95" customHeight="1">
+    <row r="3" spans="1:4" ht="28.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B14-B15,"입력 확인"),"입력 확인")</f>
         <v>-200000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:4" ht="45" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),MAX(0,B15-B14),"입력 확인"),"입력 확인")</f>
         <v>200000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="34.049999999999997" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:4" ht="45" customHeight="1">
+      <c r="A7" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B14-B15+B16,"입력 확인"),"입력 확인")</f>
         <v>1800000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1">
+    <row r="8" spans="1:4" ht="28.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1">
+    <row r="9" spans="1:4" ht="28.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1">
+    <row r="10" spans="1:4" ht="28.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1">
+    <row r="11" spans="1:4" ht="28.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="19" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1">
+    <row r="12" spans="1:4" ht="28.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1" t="e">
+      <c r="D12" s="19" t="e">
         <f>중간잔액+정산. 입금 전에 지출하는 한</f>
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4" ht="28.95" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1">
+    <row r="14" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>1000000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1">
+    <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>1200000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>2000000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" ht="25.95" customHeight="1">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="25.95" customHeight="1">
+    <row r="21" spans="1:4" ht="28.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="25.95" customHeight="1">
+    <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="25.95" customHeight="1">
+    <row r="23" spans="1:4" ht="28.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="25.95" customHeight="1">
+    <row r="24" spans="1:4" ht="28.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="25.95" customHeight="1">
+    <row r="25" spans="1:4" ht="28.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -8492,12 +9078,21 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>AND(ISNUMBER(B5),B5&lt;0)</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="21" priority="2">
+      <formula>ISTEXT(B5)</formula>
+    </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="decimal" sqref="B14:B16" xr:uid="{00000000-0002-0000-0800-000000000000}">
+      <formula1>0</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D23" location="'시작'!A1" display="← 계산 스튜디오로 돌아가기" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
   </hyperlinks>

--- a/downloads/ecommerce-calculators.xlsx
+++ b/downloads/ecommerce-calculators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yjbab\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AFA45D5-EDEA-4A15-9EC5-FCF5E7B563DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72AF3852-A9E6-489E-9E99-E8463377B9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="306">
   <si>
     <t>팔아본 팀장의 계산 스튜디오</t>
   </si>
@@ -878,6 +878,18 @@
     <t>총 매출 (원)</t>
   </si>
   <si>
+    <t>기여금 최다 상품</t>
+  </si>
+  <si>
+    <t>주문당 평균 기여금</t>
+  </si>
+  <si>
+    <t>광고 후 기여율</t>
+  </si>
+  <si>
+    <t>적자 상품 수</t>
+  </si>
+  <si>
     <t>노란 칸에 상품별 값을 입력하세요. 광고비는 같은 기간의 상품별 총액입니다.</t>
   </si>
   <si>
@@ -948,17 +960,30 @@
   </si>
   <si>
     <t>배송·포장비는 주문당 값입니다. 한 주문에 여러 상품이 있으면 비용 배분 기준을 먼저 맞추세요.</t>
+  </si>
+  <si>
+    <t>필터로 남긴 상품 합계</t>
+  </si>
+  <si>
+    <t>위 전체 합계와 구분해서 확인하세요.</t>
+  </si>
+  <si>
+    <t>기여금 최다 상품은 동률일 때 첫 상품을 표시합니다. 순이익·판매 추천 순위와는 다릅니다.</t>
+  </si>
+  <si>
+    <t>노란 입력칸만 수정 · 보호 해제는 검토 메뉴</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="177" formatCode="#,##0;[Red]\(#,##0\);0"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.00&quot; %&quot;"/>
     <numFmt numFmtId="180" formatCode="#,##0&quot; 원&quot;"/>
+    <numFmt numFmtId="181" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -1142,7 +1167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1154,9 +1179,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1210,12 +1232,6 @@
     <xf numFmtId="177" fontId="12" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1234,6 +1250,9 @@
     <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="15" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1245,6 +1264,29 @@
     </xf>
     <xf numFmtId="177" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="13" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1734,7 +1776,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5ED9-4DB6-8796-C0592B93A507}"/>
+              <c16:uniqueId val="{00000000-E4D3-49EF-B572-3B33FECCD918}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1921,7 +1963,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3FAC-4866-8B9E-12FD9E81233B}"/>
+              <c16:uniqueId val="{00000000-BDEA-4EFA-88B4-916AA619EDE5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2335,23 +2377,23 @@
     </row>
     <row r="2" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="37.950000000000003" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" ht="28.05" customHeight="1">
       <c r="A4" s="1"/>
@@ -2377,10 +2419,10 @@
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="1"/>
@@ -2389,76 +2431,76 @@
     </row>
     <row r="7" spans="1:6" ht="33" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" spans="1:6" ht="33" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" spans="1:6" ht="33" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="14"/>
     </row>
     <row r="10" spans="1:6" ht="33" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="14"/>
     </row>
     <row r="11" spans="1:6" ht="33" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="15"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" spans="1:6" ht="33" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="1"/>
@@ -2467,10 +2509,10 @@
     </row>
     <row r="13" spans="1:6" ht="33" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="1"/>
@@ -2479,10 +2521,10 @@
     </row>
     <row r="14" spans="1:6" ht="33" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>25</v>
       </c>
       <c r="D14" s="1"/>
@@ -2493,10 +2535,10 @@
     </row>
     <row r="15" spans="1:6" ht="33" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="1"/>
@@ -2505,10 +2547,10 @@
     </row>
     <row r="16" spans="1:6" ht="33" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="1"/>
@@ -2519,10 +2561,10 @@
     </row>
     <row r="17" spans="1:6" ht="33" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D17" s="1"/>
@@ -2531,10 +2573,10 @@
     </row>
     <row r="18" spans="1:6" ht="33" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="1"/>
@@ -2543,59 +2585,59 @@
     </row>
     <row r="19" spans="1:6" ht="33" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="1"/>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="17"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="1:6" ht="33" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="17"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21" spans="1:6" ht="33" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="17"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" ht="33" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>46</v>
       </c>
       <c r="D22" s="1"/>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="17"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" ht="28.05" customHeight="1">
       <c r="A23" s="1"/>
@@ -2710,12 +2752,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2733,46 +2775,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B17,1)=0,B14&gt;0,B15&lt;=B14),(B14-B15)*B16-B15*B17,"입력 확인"),"입력 확인")</f>
         <v>889000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B17,1)=0,B14&gt;0,B15&lt;=B14),B14*B16-B5,"입력 확인"),"입력 확인")</f>
         <v>81000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B17,1)=0,B14&gt;0,B15&lt;=B14),B15/B14*100,"입력 확인"),"입력 확인")</f>
         <v>5</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2780,7 +2822,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2800,7 +2842,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2808,7 +2850,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2820,7 +2862,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2828,11 +2870,11 @@
       <c r="A14" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>100</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2840,11 +2882,11 @@
       <c r="A15" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>5</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2852,39 +2894,39 @@
       <c r="A16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>9700</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="34">
         <v>6500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2892,7 +2934,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -2904,7 +2948,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2933,6 +2977,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="20" priority="1">
@@ -2976,12 +3021,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2999,46 +3044,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,B16&lt;=100),B14*B15,"입력 확인"),"입력 확인")</f>
         <v>100000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,B16&lt;=100),B5*B16/100,"입력 확인"),"입력 확인")</f>
         <v>60000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,B16&lt;=100),B5*(1-B16/100),"입력 확인"),"입력 확인")</f>
         <v>40000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3046,7 +3091,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3066,7 +3111,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3074,7 +3119,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3086,7 +3131,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>167</v>
       </c>
     </row>
@@ -3094,11 +3139,11 @@
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>100</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>169</v>
       </c>
     </row>
@@ -3106,45 +3151,45 @@
       <c r="A15" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>1000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <v>60</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3152,7 +3197,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -3164,7 +3211,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3193,6 +3240,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -3240,12 +3288,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3263,59 +3311,59 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B14*B16/100,"입력 확인"),"입력 확인")</f>
         <v>20</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B14*B15,"입력 확인"),"입력 확인")</f>
         <v>500000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B5*B17-B6,"입력 확인"),"입력 확인")</f>
         <v>100000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0,B17&gt;0),B15/B17*100,"입력 확인"),"입력 확인")</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3335,7 +3383,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3343,7 +3391,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3355,7 +3403,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>177</v>
       </c>
     </row>
@@ -3363,11 +3411,11 @@
       <c r="A14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>1000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3375,11 +3423,11 @@
       <c r="A15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>500</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>181</v>
       </c>
     </row>
@@ -3387,39 +3435,39 @@
       <c r="A16" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <v>2</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="34">
         <v>30000</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3427,7 +3475,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -3439,7 +3489,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3468,6 +3518,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="16" priority="1">
@@ -3515,12 +3566,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3538,33 +3589,33 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B14&gt;0,B16&lt;=B14),B14*B15/100,"입력 확인"),"입력 확인")</f>
         <v>194</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B14&gt;0,B16&lt;=B14),(B14-B16)*B15/100,"입력 확인"),"입력 확인")</f>
         <v>134</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3572,7 +3623,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3580,7 +3631,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3600,7 +3651,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>187</v>
       </c>
     </row>
@@ -3608,7 +3659,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>188</v>
       </c>
     </row>
@@ -3620,7 +3671,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>189</v>
       </c>
     </row>
@@ -3628,11 +3679,11 @@
       <c r="A14" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>9700</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>190</v>
       </c>
     </row>
@@ -3640,11 +3691,11 @@
       <c r="A15" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="35">
         <v>2</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>192</v>
       </c>
     </row>
@@ -3652,35 +3703,35 @@
       <c r="A16" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>3000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3688,7 +3739,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -3700,7 +3753,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3729,6 +3782,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
     <cfRule type="expression" dxfId="14" priority="1">
@@ -3776,12 +3830,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3799,33 +3853,33 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B16,1)=0,B15&gt;0,B16&gt;0),B15/B16,"입력 확인"),"입력 확인")</f>
         <v>6</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B14,1)=0,MOD(B15,1)=0,MOD(B16,1)=0,B15&gt;0,B16&gt;0),B14/B5,"입력 확인"),"입력 확인")</f>
         <v>20</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3833,7 +3887,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3841,7 +3895,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3861,7 +3915,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3869,7 +3923,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>198</v>
       </c>
     </row>
@@ -3881,7 +3935,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3889,11 +3943,11 @@
       <c r="A14" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>120</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3901,45 +3955,45 @@
       <c r="A15" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>180</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>30</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3947,7 +4001,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -3959,7 +4015,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3988,6 +4044,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
     <cfRule type="expression" dxfId="12" priority="1">
@@ -4031,12 +4088,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4054,33 +4111,33 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B15,1)=0,MOD(B16,1)=0,B14&gt;0,B15&gt;0),B14*B15,"입력 확인"),"입력 확인")</f>
         <v>60</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,MOD(B15,1)=0,MOD(B16,1)=0,B14&gt;0,B15&gt;0),ROUNDUP(ROUND(B5+B16,8),0),"입력 확인"),"입력 확인")</f>
         <v>90</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4088,7 +4145,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4096,7 +4153,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4116,7 +4173,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4124,7 +4181,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4136,7 +4193,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4144,11 +4201,11 @@
       <c r="A14" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>6</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>211</v>
       </c>
     </row>
@@ -4156,45 +4213,45 @@
       <c r="A15" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>10</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>30</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4202,7 +4259,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -4214,7 +4273,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4243,6 +4302,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
     <cfRule type="expression" dxfId="10" priority="1">
@@ -4286,12 +4346,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4309,46 +4369,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B14,"입력 확인"),"입력 확인")</f>
         <v>800000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B15-B16,"입력 확인"),"입력 확인")</f>
         <v>900000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B6-B5,"입력 확인"),"입력 확인")</f>
         <v>100000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4356,7 +4416,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4376,7 +4436,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>218</v>
       </c>
     </row>
@@ -4384,7 +4444,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>219</v>
       </c>
     </row>
@@ -4396,7 +4456,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>220</v>
       </c>
     </row>
@@ -4404,11 +4464,11 @@
       <c r="A14" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>800000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4416,45 +4476,45 @@
       <c r="A15" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>1100000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>200000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4462,7 +4522,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -4474,7 +4536,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4503,6 +4565,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -4546,12 +4609,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4569,46 +4632,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B15&lt;=100,B17&lt;=100),B14*B15/100,"입력 확인"),"입력 확인")</f>
         <v>300000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B15&lt;=100,B17&lt;=100),B16*B17/100,"입력 확인"),"입력 확인")</f>
         <v>600000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B15&lt;=100,B17&lt;=100),B6-B5,"입력 확인"),"입력 확인")</f>
         <v>300000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4616,7 +4679,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4636,7 +4699,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>229</v>
       </c>
     </row>
@@ -4644,7 +4707,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>230</v>
       </c>
     </row>
@@ -4656,7 +4719,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4664,59 +4727,59 @@
       <c r="A14" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>3000000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19"/>
+      <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="35">
         <v>10</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>2000000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="35">
         <v>30</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4724,7 +4787,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -4736,7 +4801,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4765,6 +4830,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="6" priority="1">
@@ -4812,12 +4878,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4835,46 +4901,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B17&lt;=100,MOD(B19,1)=0,B17&lt;100,B19&gt;0,B14*(1-B17/100)-B16-B18&gt;0,B15*(1-B17/100)-B16-B18&gt;0),B14*(1-B17/100)-B16-B18,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B17&lt;=100,MOD(B19,1)=0,B17&lt;100,B19&gt;0,B14*(1-B17/100)-B16-B18&gt;0,B15*(1-B17/100)-B16-B18&gt;0),B15*(1-B17/100)-B16-B18,"입력 확인"),"입력 확인")</f>
         <v>12520</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B17&lt;=100,MOD(B19,1)=0,B17&lt;100,B19&gt;0,B14*(1-B17/100)-B16-B18&gt;0,B15*(1-B17/100)-B16-B18&gt;0),ROUNDUP(ROUND(B5*B19/B6,8),0),"입력 확인"),"입력 확인")</f>
         <v>78</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4882,7 +4948,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4902,7 +4968,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>238</v>
       </c>
     </row>
@@ -4910,7 +4976,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4922,7 +4988,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>240</v>
       </c>
     </row>
@@ -4930,11 +4996,11 @@
       <c r="A14" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4942,11 +5008,11 @@
       <c r="A15" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>33000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>111</v>
       </c>
     </row>
@@ -4954,47 +5020,47 @@
       <c r="A16" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>15000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="35">
         <v>6</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="34">
         <v>3500</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="34">
         <v>100</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5002,7 +5068,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -5014,7 +5082,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -5043,6 +5111,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="4" priority="1">
@@ -5096,10 +5165,10 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="48" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -5139,15 +5208,15 @@
       <c r="A5" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="24">
         <f>IFERROR(IF(AND(COUNT(B12:B17)=6,MIN(B12:B17)&gt;=0,B14+B15&lt;100,B17&lt;100),ROUNDUP(ROUND((B12+B13)/(1-(B14+B15)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>28907</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="3">
+      <c r="D5" s="38">
         <v>5</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="26">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D5&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D5)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>20787</v>
       </c>
@@ -5159,15 +5228,15 @@
       <c r="A6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="24">
         <f>IFERROR(IF(ISNUMBER(B5),ROUNDUP(ROUND((B12+B13+B16)/(1-B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>30320</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="3">
+      <c r="D6" s="38">
         <v>10</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="26">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D6&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D6)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>22024</v>
       </c>
@@ -5179,15 +5248,15 @@
       <c r="A7" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="24">
         <f>IFERROR(ROUNDUP(ROUND(B5/(1-B17/100),8),0),"입력 확인")</f>
         <v>32119</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="3">
+      <c r="D7" s="38">
         <v>15</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="26">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D7&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D7)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>23418</v>
       </c>
@@ -5197,12 +5266,12 @@
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="27"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="3">
+      <c r="D8" s="38">
         <v>20</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="26">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D8&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D8)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>25000</v>
       </c>
@@ -5214,10 +5283,10 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="3">
+      <c r="D9" s="38">
         <v>25</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="26">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D9&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D9)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>26812</v>
       </c>
@@ -5229,10 +5298,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="3">
+      <c r="D10" s="38">
         <v>30</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="26">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D10&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D10)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>28907</v>
       </c>
@@ -5248,10 +5317,10 @@
         <v>51</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="3">
+      <c r="D11" s="38">
         <v>35</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="26">
         <f>IFERROR(IF(AND(ISNUMBER(B5),$B$14+D11&lt;100),ROUNDUP(ROUND(($B$12+$B$13)/(1-($B$14+D11)/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>31356</v>
       </c>
@@ -5263,7 +5332,7 @@
       <c r="A12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="37">
         <v>15000</v>
       </c>
       <c r="C12" s="1"/>
@@ -5277,7 +5346,7 @@
       <c r="A13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="37">
         <v>3500</v>
       </c>
       <c r="C13" s="1"/>
@@ -5291,7 +5360,7 @@
       <c r="A14" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="37">
         <v>6</v>
       </c>
       <c r="C14" s="1"/>
@@ -5305,7 +5374,7 @@
       <c r="A15" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="37">
         <v>30</v>
       </c>
       <c r="C15" s="1"/>
@@ -5319,7 +5388,7 @@
       <c r="A16" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="37">
         <v>10000</v>
       </c>
       <c r="C16" s="1"/>
@@ -5333,7 +5402,7 @@
       <c r="A17" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="37">
         <v>10</v>
       </c>
       <c r="C17" s="1"/>
@@ -5345,7 +5414,7 @@
     </row>
     <row r="18" spans="1:8" ht="28.05" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="28"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -5355,7 +5424,7 @@
     </row>
     <row r="19" spans="1:8" ht="28.05" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="28"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -5364,10 +5433,10 @@
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="B20" s="19"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -5376,10 +5445,10 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -5388,8 +5457,8 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -5398,8 +5467,8 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -5578,6 +5647,7 @@
       <c r="H40" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="2" priority="1">
@@ -5610,12 +5680,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5633,33 +5703,33 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0),(B14-B15)/B14*100,"입력 확인"),"입력 확인")</f>
         <v>50</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B17)=4,MIN(B14:B17)&gt;=0,B16&lt;=100,B14&gt;0),B14-B15-B14*B16/100-B17,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
@@ -5667,7 +5737,7 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5675,7 +5745,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -5695,7 +5765,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5703,7 +5773,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5715,7 +5785,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>63</v>
       </c>
     </row>
@@ -5723,59 +5793,59 @@
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19"/>
+      <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="34">
         <v>3500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5783,7 +5853,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -5795,7 +5867,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -5824,6 +5896,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B6">
     <cfRule type="expression" dxfId="36" priority="1">
@@ -5874,10 +5947,10 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="48" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -5917,15 +5990,15 @@
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="24">
         <f>IFERROR(IF(AND(COUNT(B13:B19)=7,MIN(B13:B19)&gt;=0,B15&lt;100,MOD(B19,1)=0),B13*(1-B15/100)-B14-B16,"입력 확인"),"입력 확인")</f>
         <v>6880</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="3">
+      <c r="D5" s="38">
         <v>25</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="26">
         <f t="shared" ref="E5:E10" si="0">IFERROR($B$5*D5-$B$17,"입력 확인")</f>
         <v>-28000</v>
       </c>
@@ -5937,15 +6010,15 @@
       <c r="A6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="24">
         <f>IFERROR(IF(B5&gt;0,ROUNDUP(ROUND(B17/B5,8),0),"기여금 양수 필요"),"입력 확인")</f>
         <v>30</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="3">
+      <c r="D6" s="38">
         <v>50</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="26">
         <f t="shared" si="0"/>
         <v>144000</v>
       </c>
@@ -5957,15 +6030,15 @@
       <c r="A7" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="24">
         <f>IFERROR(IF(B5&gt;0,ROUNDUP(ROUND((B17+B18)/B5,8),0),"기여금 양수 필요"),"입력 확인")</f>
         <v>73</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="3">
+      <c r="D7" s="38">
         <v>75</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="26">
         <f t="shared" si="0"/>
         <v>316000</v>
       </c>
@@ -5977,15 +6050,15 @@
       <c r="A8" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="24">
         <f>IFERROR(B5*B19-B17,"입력 확인")</f>
         <v>488000</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="3">
+      <c r="D8" s="38">
         <v>100</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="26">
         <f t="shared" si="0"/>
         <v>488000</v>
       </c>
@@ -5997,10 +6070,10 @@
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="3">
+      <c r="D9" s="38">
         <v>125</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="26">
         <f t="shared" si="0"/>
         <v>660000</v>
       </c>
@@ -6012,10 +6085,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="3">
+      <c r="D10" s="38">
         <v>150</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="26">
         <f t="shared" si="0"/>
         <v>832000</v>
       </c>
@@ -6028,7 +6101,7 @@
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="29"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -6037,7 +6110,7 @@
       <c r="A12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="27" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="1"/>
@@ -6051,7 +6124,7 @@
       <c r="A13" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="37">
         <v>27000</v>
       </c>
       <c r="C13" s="1"/>
@@ -6065,7 +6138,7 @@
       <c r="A14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="37">
         <v>15000</v>
       </c>
       <c r="C14" s="1"/>
@@ -6079,7 +6152,7 @@
       <c r="A15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="37">
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
@@ -6093,7 +6166,7 @@
       <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="37">
         <v>3500</v>
       </c>
       <c r="C16" s="1"/>
@@ -6107,7 +6180,7 @@
       <c r="A17" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="37">
         <v>200000</v>
       </c>
       <c r="C17" s="1"/>
@@ -6121,7 +6194,7 @@
       <c r="A18" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="37">
         <v>300000</v>
       </c>
       <c r="C18" s="1"/>
@@ -6135,7 +6208,7 @@
       <c r="A19" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="37">
         <v>100</v>
       </c>
       <c r="C19" s="1"/>
@@ -6146,8 +6219,8 @@
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -6156,8 +6229,8 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -6166,10 +6239,10 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="B22" s="19"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -6178,10 +6251,10 @@
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" ht="28.05" customHeight="1">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="B23" s="19"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -6360,6 +6433,7 @@
       <c r="H40" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -6400,20 +6474,20 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="43.95" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="28.05" customHeight="1">
@@ -6436,7 +6510,7 @@
         <v>272</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="31">
+      <c r="C4" s="29">
         <f>IF(COUNT(L10:L19)=10,SUM(L10:L19),"입력 확인")</f>
         <v>8930000</v>
       </c>
@@ -6445,29 +6519,49 @@
         <v>273</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="31">
+      <c r="G4" s="29">
         <f>IF(COUNT(J10:J19)=10,SUM(J10:J19),"입력 확인")</f>
         <v>34500000</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="str">
+        <f>IF(COUNT(L10:L19)=10,INDEX(A10:A19,MATCH(MAX(L10:L19),L10:L19,0)),"입력 확인")</f>
+        <v>예시 상품 10</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>275</v>
+      </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="28">
+        <f>IFERROR(IF(COUNT(L10:L19)=10,SUM(L10:L19)/SUM(F10:F19),"입력 확인"),"주문 수 확인")</f>
+        <v>8930</v>
+      </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="33">
+        <f>IFERROR(C4/G4,"매출 확인")</f>
+        <v>0.2588405797101449</v>
+      </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1">
+        <f>IF(COUNT(L10:L19)=10,COUNTIF(L10:L19,"&lt;0"),"입력 확인")</f>
+        <v>0</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
@@ -6488,7 +6582,7 @@
     </row>
     <row r="7" spans="1:13" ht="28.05" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -6519,479 +6613,479 @@
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1">
-      <c r="A9" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="E9" s="32" t="s">
+      <c r="A9" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="C9" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="D9" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="E9" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="F9" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="G9" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="H9" s="30" t="s">
         <v>286</v>
       </c>
+      <c r="I9" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>290</v>
+      </c>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="33" customHeight="1">
-      <c r="A10" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="B10" s="34">
+      <c r="A10" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="32">
         <v>30000</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="32">
         <v>15000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="32">
         <v>6</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="32">
         <v>3500</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="32">
         <v>100</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="32">
         <v>500000</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <f t="shared" ref="H10:H19" si="0">IFERROR(IF(AND(COUNT(B10:G10)=6,MIN(B10:G10)&gt;=0,B10&gt;0,D10&lt;100,MOD(F10,1)=0),B10*(1-D10/100)-C10-E10,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <f t="shared" ref="I10:I19" si="1">IFERROR(H10/B10*100,"입력 확인")</f>
         <v>32.333333333333329</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <f t="shared" ref="J10:J19" si="2">IFERROR(IF(ISNUMBER(H10),B10*F10,"입력 확인"),"입력 확인")</f>
         <v>3000000</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <f t="shared" ref="K10:K19" si="3">IFERROR(H10*F10,"입력 확인")</f>
         <v>970000</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <f t="shared" ref="L10:L19" si="4">IFERROR(K10-G10,"입력 확인")</f>
         <v>470000</v>
       </c>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" ht="33" customHeight="1">
-      <c r="A11" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="34">
+      <c r="A11" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" s="32">
         <v>31000</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="32">
         <v>15000</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="32">
         <v>6</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="32">
         <v>3500</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="32">
         <v>100</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="32">
         <v>500000</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <f t="shared" si="0"/>
         <v>10640</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <f t="shared" si="1"/>
         <v>34.322580645161288</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <f t="shared" si="2"/>
         <v>3100000</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <f t="shared" si="3"/>
         <v>1064000</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <f t="shared" si="4"/>
         <v>564000</v>
       </c>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13" ht="33" customHeight="1">
-      <c r="A12" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="B12" s="34">
+      <c r="A12" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B12" s="32">
         <v>32000</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="32">
         <v>15000</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="32">
         <v>6</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="32">
         <v>3500</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="32">
         <v>100</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="32">
         <v>500000</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <f t="shared" si="0"/>
         <v>11580</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <f t="shared" si="1"/>
         <v>36.1875</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <f t="shared" si="2"/>
         <v>3200000</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <f t="shared" si="3"/>
         <v>1158000</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <f t="shared" si="4"/>
         <v>658000</v>
       </c>
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13" ht="33" customHeight="1">
-      <c r="A13" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="34">
+      <c r="A13" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B13" s="32">
         <v>33000</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="32">
         <v>15000</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="32">
         <v>6</v>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="32">
         <v>3500</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="32">
         <v>100</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="32">
         <v>500000</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <f t="shared" si="0"/>
         <v>12520</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <f t="shared" si="1"/>
         <v>37.939393939393938</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="5">
         <f t="shared" si="2"/>
         <v>3300000</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <f t="shared" si="3"/>
         <v>1252000</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <f t="shared" si="4"/>
         <v>752000</v>
       </c>
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:13" ht="33" customHeight="1">
-      <c r="A14" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="B14" s="34">
+      <c r="A14" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="B14" s="32">
         <v>34000</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="32">
         <v>15000</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="32">
         <v>6</v>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="32">
         <v>3500</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="32">
         <v>100</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="32">
         <v>500000</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <f t="shared" si="0"/>
         <v>13460</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <f t="shared" si="1"/>
         <v>39.588235294117645</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <f t="shared" si="2"/>
         <v>3400000</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <f t="shared" si="3"/>
         <v>1346000</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <f t="shared" si="4"/>
         <v>846000</v>
       </c>
       <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:13" ht="33" customHeight="1">
-      <c r="A15" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="B15" s="34">
+      <c r="A15" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B15" s="32">
         <v>35000</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="32">
         <v>15000</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="32">
         <v>6</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="32">
         <v>3500</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="32">
         <v>100</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="32">
         <v>500000</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <f t="shared" si="0"/>
         <v>14400</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="6">
         <f t="shared" si="1"/>
         <v>41.142857142857139</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <f t="shared" si="2"/>
         <v>3500000</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <f t="shared" si="3"/>
         <v>1440000</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <f t="shared" si="4"/>
         <v>940000</v>
       </c>
       <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:13" ht="33" customHeight="1">
-      <c r="A16" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="B16" s="34">
+      <c r="A16" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="B16" s="32">
         <v>36000</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="32">
         <v>15000</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="32">
         <v>6</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="32">
         <v>3500</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="32">
         <v>100</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="32">
         <v>500000</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <f t="shared" si="0"/>
         <v>15340</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="6">
         <f t="shared" si="1"/>
         <v>42.611111111111114</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <f t="shared" si="2"/>
         <v>3600000</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <f t="shared" si="3"/>
         <v>1534000</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <f t="shared" si="4"/>
         <v>1034000</v>
       </c>
       <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13" ht="33" customHeight="1">
-      <c r="A17" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="B17" s="34">
+      <c r="A17" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" s="32">
         <v>37000</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="32">
         <v>15000</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="32">
         <v>6</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="32">
         <v>3500</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="32">
         <v>100</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="32">
         <v>500000</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <f t="shared" si="0"/>
         <v>16280</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="6">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="5">
         <f t="shared" si="2"/>
         <v>3700000</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <f t="shared" si="3"/>
         <v>1628000</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <f t="shared" si="4"/>
         <v>1128000</v>
       </c>
       <c r="M17" s="1"/>
     </row>
     <row r="18" spans="1:13" ht="33" customHeight="1">
-      <c r="A18" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="B18" s="34">
+      <c r="A18" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="B18" s="32">
         <v>38000</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="32">
         <v>15000</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="32">
         <v>6</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="32">
         <v>3500</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="32">
         <v>100</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="32">
         <v>500000</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <f t="shared" si="0"/>
         <v>17220</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="6">
         <f t="shared" si="1"/>
         <v>45.315789473684212</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="5">
         <f t="shared" si="2"/>
         <v>3800000</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <f t="shared" si="3"/>
         <v>1722000</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <f t="shared" si="4"/>
         <v>1222000</v>
       </c>
       <c r="M18" s="1"/>
     </row>
     <row r="19" spans="1:13" ht="33" customHeight="1">
-      <c r="A19" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="34">
+      <c r="A19" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="B19" s="32">
         <v>39000</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="32">
         <v>15000</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="32">
         <v>6</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="32">
         <v>3500</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="32">
         <v>100</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="32">
         <v>500000</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <f t="shared" si="0"/>
         <v>18160</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <f t="shared" si="1"/>
         <v>46.564102564102569</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="5">
         <f t="shared" si="2"/>
         <v>3900000</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <f t="shared" si="3"/>
         <v>1816000</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <f t="shared" si="4"/>
         <v>1316000</v>
       </c>
@@ -7029,7 +7123,7 @@
     </row>
     <row r="22" spans="1:13" ht="28.05" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -7060,11 +7154,18 @@
       <c r="M23" s="1"/>
     </row>
     <row r="24" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="C24" s="28">
+        <f>SUBTOTAL(109,L10:L19)</f>
+        <v>8930000</v>
+      </c>
       <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>303</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -7090,7 +7191,9 @@
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="28.05" customHeight="1">
-      <c r="A26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>304</v>
+      </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -7209,12 +7312,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7232,46 +7335,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,B18&lt;=100,MOD(B19,1)=0,B14&gt;0,B18&lt;100,B14-B15-B14*B16/100-B17&gt;0,B14*(1-B18/100)*(1-B16/100)-B15-B17&gt;0),B14-B15-B14*B16/100-B17,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,B18&lt;=100,MOD(B19,1)=0,B14&gt;0,B18&lt;100,B14-B15-B14*B16/100-B17&gt;0,B14*(1-B18/100)*(1-B16/100)-B15-B17&gt;0),B14*(1-B18/100)*(1-B16/100)-B15-B17,"입력 확인"),"입력 확인")</f>
         <v>6880</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,B18&lt;=100,MOD(B19,1)=0,B14&gt;0,B18&lt;100,B14-B15-B14*B16/100-B17&gt;0,B14*(1-B18/100)*(1-B16/100)-B15-B17&gt;0),ROUNDUP(ROUND(B5*B19/B6,8),0),"입력 확인"),"입력 확인")</f>
         <v>141</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -7279,7 +7382,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7299,7 +7402,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7307,7 +7410,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>75</v>
       </c>
     </row>
@@ -7319,7 +7422,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>76</v>
       </c>
     </row>
@@ -7327,11 +7430,11 @@
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>77</v>
       </c>
     </row>
@@ -7339,57 +7442,57 @@
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="34">
         <v>3500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="35">
         <v>10</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="34">
         <v>100</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -7397,7 +7500,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -7409,7 +7514,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -7438,6 +7543,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="34" priority="1">
@@ -7485,12 +7591,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7508,59 +7614,59 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),B15*B14/100,"입력 확인"),"입력 확인")</f>
         <v>9699</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),B5-B16,"입력 확인"),"입력 확인")</f>
         <v>2199</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),10000/B14,"입력 확인"),"입력 확인")</f>
         <v>309.31023816888342</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B14&lt;=100,B14&gt;0,B16&gt;0),B15/B16*100,"입력 확인"),"입력 확인")</f>
         <v>400</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7580,7 +7686,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>85</v>
       </c>
     </row>
@@ -7588,7 +7694,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>86</v>
       </c>
     </row>
@@ -7600,7 +7706,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7608,55 +7714,55 @@
       <c r="A14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="35">
         <v>32.33</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19"/>
+      <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>30000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>7500</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -7664,7 +7770,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -7676,7 +7784,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -7705,6 +7813,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="32" priority="1">
@@ -7752,12 +7861,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -7775,59 +7884,59 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),ROUNDUP(ROUND((B17+B15+B16)/(B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>30000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),ROUNDUP(ROUND(B18+B19/(B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>28572</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),ROUNDUP(ROUND(B19/(B14/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>8572</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B14&lt;=100,B14&gt;0),B18*B14/100+B19-B15-B16,"입력 확인"),"입력 확인")</f>
         <v>6500</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -7847,7 +7956,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7855,7 +7964,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>95</v>
       </c>
     </row>
@@ -7867,7 +7976,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>96</v>
       </c>
     </row>
@@ -7875,67 +7984,67 @@
       <c r="A14" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="35">
         <v>35</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19"/>
+      <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>3000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>500</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="34">
         <v>7000</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="34">
         <v>20000</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="34">
         <v>3000</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -7943,7 +8052,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -7955,7 +8066,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -7984,6 +8095,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="30" priority="1">
@@ -8031,12 +8143,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8054,46 +8166,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100),B14-B15-B14*B16/100-B17-B18,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100),B19-B15-B17-B18,"입력 확인"),"입력 확인")</f>
         <v>9700</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100),B14-B14*B16/100-B19,"입력 확인"),"입력 확인")</f>
         <v>0</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -8101,7 +8213,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -8121,7 +8233,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>107</v>
       </c>
     </row>
@@ -8129,7 +8241,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>108</v>
       </c>
     </row>
@@ -8141,7 +8253,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>109</v>
       </c>
     </row>
@@ -8149,11 +8261,11 @@
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>110</v>
       </c>
     </row>
@@ -8161,11 +8273,11 @@
       <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>111</v>
       </c>
     </row>
@@ -8173,47 +8285,47 @@
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="34">
         <v>3000</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="34">
         <v>500</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="34">
         <v>28200</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -8221,7 +8333,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -8233,7 +8347,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -8262,6 +8376,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="28" priority="1">
@@ -8309,12 +8424,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8332,59 +8447,59 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),B18*(B14*(1-B16/100)-B15-B17),"입력 확인"),"입력 확인")</f>
         <v>19400</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),B19*(1-B16/100)-B18*B15-B17,"입력 확인"),"입력 확인")</f>
         <v>20080</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),B6-B5,"입력 확인"),"입력 확인")</f>
         <v>680</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B19)=6,MIN(B14:B19)&gt;=0,B16&lt;=100,MOD(B18,1)=0,B16&lt;100,B18&gt;=2,MOD(B18,1)=0),ROUNDUP(ROUND((B5+B18*B15+B17)/(1-B16/100),8),0),"입력 확인"),"입력 확인")</f>
         <v>56277</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -8404,7 +8519,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>118</v>
       </c>
     </row>
@@ -8412,7 +8527,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>119</v>
       </c>
     </row>
@@ -8424,7 +8539,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>120</v>
       </c>
     </row>
@@ -8432,11 +8547,11 @@
       <c r="A14" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>122</v>
       </c>
     </row>
@@ -8444,11 +8559,11 @@
       <c r="A15" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>15000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>124</v>
       </c>
     </row>
@@ -8456,11 +8571,11 @@
       <c r="A16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>111</v>
       </c>
     </row>
@@ -8468,37 +8583,37 @@
       <c r="A17" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="34">
         <v>3500</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="34">
         <v>2</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="34">
         <v>57000</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -8506,7 +8621,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -8518,7 +8635,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -8547,6 +8664,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="expression" dxfId="26" priority="1">
@@ -8594,12 +8712,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8617,46 +8735,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B16&lt;=100,B14&gt;0,B15+B16&lt;=100),B14*(1-B15/100)*(1-B16/100),"입력 확인"),"입력 확인")</f>
         <v>24300</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B16&lt;=100,B14&gt;0,B15+B16&lt;=100),B14*(1-(B15+B16)/100),"입력 확인"),"입력 확인")</f>
         <v>24000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0,B15&lt;=100,B16&lt;=100,B14&gt;0,B15+B16&lt;=100),(1-(1-B15/100)*(1-B16/100))*100,"입력 확인"),"입력 확인")</f>
         <v>18.999999999999993</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -8664,7 +8782,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -8684,7 +8802,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>132</v>
       </c>
     </row>
@@ -8692,7 +8810,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>133</v>
       </c>
     </row>
@@ -8704,7 +8822,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="e">
+      <c r="D13" s="18" t="e">
         <v>#NAME?</v>
       </c>
     </row>
@@ -8712,11 +8830,11 @@
       <c r="A14" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>30000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>135</v>
       </c>
     </row>
@@ -8724,11 +8842,11 @@
       <c r="A15" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="35">
         <v>10</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>137</v>
       </c>
     </row>
@@ -8736,35 +8854,35 @@
       <c r="A16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="35">
         <v>10</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -8772,7 +8890,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -8784,7 +8904,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -8813,6 +8933,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="24" priority="1">
@@ -8860,12 +8981,12 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="46.05" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="8"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8883,46 +9004,46 @@
         <v>51</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B14-B15,"입력 확인"),"입력 확인")</f>
         <v>-200000</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="22" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),MAX(0,B15-B14),"입력 확인"),"입력 확인")</f>
         <v>200000</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="21">
         <f>IFERROR(IF(AND(COUNT(B14:B16)=3,MIN(B14:B16)&gt;=0),B14-B15+B16,"입력 확인"),"입력 확인")</f>
         <v>1800000</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -8930,7 +9051,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -8950,7 +9071,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>143</v>
       </c>
     </row>
@@ -8958,7 +9079,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="19" t="e">
+      <c r="D12" s="18" t="e">
         <f>중간잔액+정산. 입금 전에 지출하는 한</f>
         <v>#NAME?</v>
       </c>
@@ -8971,7 +9092,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>144</v>
       </c>
     </row>
@@ -8979,11 +9100,11 @@
       <c r="A14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="34">
         <v>1000000</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8991,45 +9112,45 @@
       <c r="A15" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="34">
         <v>1200000</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" ht="37.049999999999997" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="34">
         <v>2000000</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="28.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:4" ht="28.95" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="19"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:4" ht="28.95" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="19"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="1:4" ht="28.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -9037,7 +9158,9 @@
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="16" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="28.95" customHeight="1">
       <c r="A22" s="1"/>
@@ -9049,7 +9172,7 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>69</v>
       </c>
     </row>
@@ -9078,6 +9201,7 @@
       <c r="D27" s="1"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="B5:B7">
     <cfRule type="expression" dxfId="22" priority="1">
